--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="SkillData" sheetId="1" r:id="rId1"/>
+    <sheet name="PackageSetData" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -80,6 +80,18 @@
   </si>
   <si>
     <t>IceBox</t>
+  </si>
+  <si>
+    <t>草料槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>水槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>产物蓝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -418,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H6"/>
+  <dimension ref="A2:H9"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="12.875" style="1"/>
@@ -554,6 +566,84 @@
         <v>2</v>
       </c>
     </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>5</v>
+      </c>
+      <c r="F7" s="1">
+        <v>100</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="1">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1">
+        <v>100</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>12</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>5</v>
+      </c>
+      <c r="F9" s="1">
+        <v>100</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -92,6 +92,19 @@
   <si>
     <t>产物蓝</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>singleCase</t>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+  </si>
+  <si>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>initItems</t>
   </si>
 </sst>
 </file>
@@ -141,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -150,6 +163,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -430,13 +447,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="12.875" style="1"/>
+    <col min="1" max="9" width="12.875" style="1"/>
+    <col min="10" max="10" width="12.875" style="4"/>
+    <col min="11" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -461,8 +480,14 @@
       <c r="H2" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="I2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -487,8 +512,14 @@
       <c r="H3" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="I3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -513,8 +544,14 @@
       <c r="H4" s="1">
         <v>0</v>
       </c>
+      <c r="I4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -539,8 +576,11 @@
       <c r="H5" s="1">
         <v>1</v>
       </c>
+      <c r="I5" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -565,8 +605,11 @@
       <c r="H6" s="1">
         <v>2</v>
       </c>
+      <c r="I6" s="1" t="b">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -591,8 +634,11 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
+      <c r="I7" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>11</v>
       </c>
@@ -617,8 +663,11 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
+      <c r="I8" s="1" t="b">
+        <v>1</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>12</v>
       </c>
@@ -641,6 +690,9 @@
         <v>15</v>
       </c>
       <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -18,8 +18,67 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>作者</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>全部, 鲜活, 非鲜活,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>作者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+Default=0,OnlyPut=1,OnlyGet=2</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -100,18 +159,29 @@
     <t>List&lt;int2&gt;</t>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>initItems</t>
+  </si>
+  <si>
+    <t>moveItemType</t>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limitItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1|100,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,6 +202,27 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -446,16 +537,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:L9"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="12.875" style="1"/>
-    <col min="10" max="10" width="12.875" style="4"/>
-    <col min="11" max="16384" width="12.875" style="1"/>
+    <col min="1" max="11" width="12.875" style="1"/>
+    <col min="12" max="12" width="12.875" style="4"/>
+    <col min="13" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -481,13 +572,19 @@
         <v>3</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -513,13 +610,19 @@
         <v>11</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
+      <c r="K3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -544,14 +647,17 @@
       <c r="H4" s="1">
         <v>0</v>
       </c>
-      <c r="I4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>23</v>
+      <c r="I4" s="1">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -576,11 +682,14 @@
       <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1" t="b">
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -605,11 +714,14 @@
       <c r="H6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1" t="b">
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -634,11 +746,17 @@
       <c r="H7" s="1">
         <v>0</v>
       </c>
-      <c r="I7" s="1" t="b">
-        <v>1</v>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>11</v>
       </c>
@@ -663,11 +781,14 @@
       <c r="H8" s="1">
         <v>0</v>
       </c>
-      <c r="I8" s="1" t="b">
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>12</v>
       </c>
@@ -692,13 +813,17 @@
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="b">
-        <v>0</v>
+      <c r="I9" s="1">
+        <v>2</v>
+      </c>
+      <c r="J9" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -173,7 +173,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1|100,4</t>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1|100,4|11,18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -24,7 +24,7 @@
     <author>作者</author>
   </authors>
   <commentList>
-    <comment ref="H3" authorId="0" shapeId="0">
+    <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -48,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0">
+    <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -174,6 +174,10 @@
   </si>
   <si>
     <t>1001,6|1002,4|2000,1|1104,4|2001,1|100,4|11,18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>maxLevel</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -538,15 +542,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L9"/>
+  <dimension ref="A2:M9"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="11" width="12.875" style="1"/>
-    <col min="12" max="12" width="12.875" style="4"/>
-    <col min="13" max="16384" width="12.875" style="1"/>
+    <col min="1" max="5" width="12.875" style="1"/>
+    <col min="6" max="6" width="11.625" style="1" customWidth="1"/>
+    <col min="7" max="12" width="12.875" style="1"/>
+    <col min="13" max="13" width="12.875" style="4"/>
+    <col min="14" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,25 +572,28 @@
         <v>3</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I2" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -598,31 +607,34 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -636,28 +648,31 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1">
+        <v>5</v>
+      </c>
+      <c r="G4" s="1">
         <v>100</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="1">
-        <v>0</v>
-      </c>
       <c r="I4" s="1">
         <v>0</v>
       </c>
-      <c r="J4" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" s="5" t="s">
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -671,25 +686,28 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="1">
+        <v>5</v>
+      </c>
+      <c r="G5" s="1">
         <v>100</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
       <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -703,25 +721,28 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="1">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1">
         <v>100</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="b">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -735,28 +756,31 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7" s="1">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1">
         <v>100</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
       <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="J7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>11</v>
       </c>
@@ -770,25 +794,28 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1">
         <v>100</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
       <c r="I8" s="1">
         <v>0</v>
       </c>
-      <c r="J8" s="1" t="b">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>12</v>
       </c>
@@ -802,21 +829,24 @@
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
         <v>100</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="1">
-        <v>0</v>
-      </c>
       <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
         <v>2</v>
       </c>
-      <c r="J9" s="1" t="b">
+      <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -173,11 +173,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1|100,4|11,18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>maxLevel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -607,7 +607,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -669,7 +669,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -177,7 +177,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2</t>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -178,6 +178,10 @@
   </si>
   <si>
     <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴棚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -249,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -262,6 +266,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -542,12 +549,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M9"/>
+  <dimension ref="A2:M10"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="12.875" style="1"/>
     <col min="6" max="6" width="11.625" style="1" customWidth="1"/>
-    <col min="7" max="12" width="12.875" style="1"/>
+    <col min="7" max="11" width="12.875" style="1"/>
+    <col min="12" max="12" width="18.875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.875" style="4"/>
     <col min="14" max="16384" width="12.875" style="1"/>
   </cols>
@@ -848,6 +856,44 @@
       </c>
       <c r="K9" s="1" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1">
+        <v>4</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6">
+        <v>100101102103105</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,6 +182,17 @@
   </si>
   <si>
     <t>柴棚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>objPackageAnimationDataId</t>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100,101,102,103,105</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -266,8 +277,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,18 +560,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:M10"/>
+  <dimension ref="A2:N10"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="12.875" style="1"/>
     <col min="6" max="6" width="11.625" style="1" customWidth="1"/>
-    <col min="7" max="11" width="12.875" style="1"/>
-    <col min="12" max="12" width="18.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="4"/>
-    <col min="14" max="16384" width="12.875" style="1"/>
+    <col min="7" max="12" width="12.875" style="1"/>
+    <col min="13" max="13" width="18.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.875" style="4"/>
+    <col min="15" max="16384" width="12.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -595,13 +606,16 @@
         <v>6</v>
       </c>
       <c r="L2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -636,13 +650,16 @@
         <v>21</v>
       </c>
       <c r="L3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -676,11 +693,14 @@
       <c r="K4" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2</v>
       </c>
@@ -714,8 +734,11 @@
       <c r="K5" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>3</v>
       </c>
@@ -749,8 +772,11 @@
       <c r="K6" s="1" t="b">
         <v>0</v>
       </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>10</v>
       </c>
@@ -785,10 +811,13 @@
         <v>1</v>
       </c>
       <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>11</v>
       </c>
@@ -822,8 +851,11 @@
       <c r="K8" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>12</v>
       </c>
@@ -857,8 +889,11 @@
       <c r="K9" s="1" t="b">
         <v>1</v>
       </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>13</v>
       </c>
@@ -892,8 +927,11 @@
       <c r="K10" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="L10" s="6">
-        <v>100101102103105</v>
+      <c r="L10" s="1">
+        <v>4</v>
+      </c>
+      <c r="M10" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -177,10 +177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>柴棚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -193,6 +189,10 @@
   </si>
   <si>
     <t>100,101,102,103,105</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -563,9 +563,9 @@
   <dimension ref="A2:N10"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="5" width="12.875" style="1"/>
-    <col min="6" max="6" width="11.625" style="1" customWidth="1"/>
-    <col min="7" max="12" width="12.875" style="1"/>
+    <col min="1" max="4" width="12.875" style="1"/>
+    <col min="5" max="10" width="9.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="12.875" style="1"/>
     <col min="13" max="13" width="18.875" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.875" style="4"/>
     <col min="15" max="16384" width="12.875" style="1"/>
@@ -606,7 +606,7 @@
         <v>6</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M2" s="6" t="s">
         <v>25</v>
@@ -650,7 +650,7 @@
         <v>21</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>26</v>
@@ -697,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -898,7 +898,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
@@ -931,7 +931,7 @@
         <v>4</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -667,16 +667,16 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>3</v>
+      </c>
+      <c r="F4" s="1">
         <v>10</v>
-      </c>
-      <c r="D4" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1">
-        <v>3</v>
-      </c>
-      <c r="F4" s="1">
-        <v>5</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
@@ -708,16 +708,16 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>3</v>
+      </c>
+      <c r="F5" s="1">
         <v>10</v>
-      </c>
-      <c r="D5" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1">
-        <v>3</v>
-      </c>
-      <c r="F5" s="1">
-        <v>5</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
@@ -746,16 +746,16 @@
         <v>14</v>
       </c>
       <c r="C6" s="1">
+        <v>20</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1">
         <v>10</v>
-      </c>
-      <c r="D6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>3</v>
-      </c>
-      <c r="F6" s="1">
-        <v>5</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -192,7 +192,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8</t>
+    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -128,10 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>杂物箱</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Bag</t>
   </si>
   <si>
@@ -193,6 +189,20 @@
   </si>
   <si>
     <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPC背包</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>储物箱(银)</t>
+  </si>
+  <si>
+    <t>储物箱(金)</t>
+  </si>
+  <si>
+    <t>储物箱(木)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -560,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:N10"/>
+  <dimension ref="A2:N13"/>
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="12.875" style="1"/>
@@ -606,13 +616,13 @@
         <v>6</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -629,7 +639,7 @@
         <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -644,19 +654,19 @@
         <v>11</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -682,7 +692,7 @@
         <v>100</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" s="1">
         <v>0</v>
@@ -697,7 +707,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -723,7 +733,7 @@
         <v>100</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
@@ -743,7 +753,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C6" s="1">
         <v>20</v>
@@ -761,10 +771,10 @@
         <v>100</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
@@ -775,25 +785,26 @@
       <c r="L6" s="1">
         <v>0</v>
       </c>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="1">
+        <v>20</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1">
         <v>10</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="1">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>3</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5</v>
       </c>
       <c r="G7" s="1">
         <v>100</v>
@@ -802,30 +813,27 @@
         <v>15</v>
       </c>
       <c r="I7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="b">
         <v>1</v>
@@ -834,7 +842,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>100</v>
@@ -843,13 +851,13 @@
         <v>15</v>
       </c>
       <c r="I8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -857,37 +865,37 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1">
         <v>20</v>
       </c>
-      <c r="C9" s="1">
-        <v>5</v>
-      </c>
       <c r="D9" s="1" t="b">
         <v>1</v>
       </c>
       <c r="E9" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="I9" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -895,43 +903,160 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
+        <v>10</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="1">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>3</v>
+      </c>
+      <c r="F10" s="1">
+        <v>5</v>
+      </c>
+      <c r="G10" s="1">
+        <v>100</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3</v>
+      </c>
+      <c r="F11" s="1">
+        <v>5</v>
+      </c>
+      <c r="G11" s="1">
+        <v>100</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>12</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2</v>
+      </c>
+      <c r="K12" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
         <v>4</v>
       </c>
-      <c r="D10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="1">
+      <c r="D13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="1">
         <v>2</v>
       </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="1">
         <v>4</v>
       </c>
-      <c r="M10" s="4" t="s">
-        <v>31</v>
+      <c r="M13" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -32,6 +32,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>全部, 鲜活, 非鲜活,</t>
@@ -41,6 +42,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -66,6 +68,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -188,10 +191,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,6|1002,4|2000,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>NPC背包</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -203,6 +202,10 @@
   </si>
   <si>
     <t>储物箱(木)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1700,1|1701,1|1702,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -210,7 +213,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,13 +239,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -707,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -753,7 +750,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1">
         <v>20</v>
@@ -792,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="1">
         <v>20</v>
@@ -830,7 +827,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="1">
         <v>20</v>
@@ -868,7 +865,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1">
         <v>20</v>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -205,7 +205,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1700,1|1701,1|1702,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1</t>
+    <t>1700,1|1701,1|1702,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1|1604,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -205,7 +205,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1700,1|1701,1|1702,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1|1604,1</t>
+    <t>3111,2|1701,1|1702,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1|1604,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1059,7 +1059,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -202,10 +202,6 @@
   </si>
   <si>
     <t>储物箱(木)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3111,2|1701,1|1702,1|1104,4|2001,1|2004,1|12,2|102,6|104,4|11,8|1660,1|1604,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -703,9 +699,7 @@
       <c r="L4" s="1">
         <v>0</v>
       </c>
-      <c r="N4" s="5" t="s">
-        <v>35</v>
-      </c>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1">

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -567,7 +567,9 @@
   <sheetFormatPr defaultColWidth="12.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="12.875" style="1"/>
-    <col min="5" max="10" width="9.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
+    <col min="7" max="10" width="9.5" style="1" customWidth="1"/>
     <col min="11" max="12" width="12.875" style="1"/>
     <col min="13" max="13" width="18.875" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.875" style="4"/>
@@ -679,7 +681,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
@@ -718,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
@@ -756,7 +758,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -795,7 +797,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7" s="1">
         <v>100</v>
@@ -833,7 +835,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
         <v>100</v>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -678,10 +678,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
@@ -717,10 +717,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
@@ -755,10 +755,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -794,10 +794,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>100</v>
@@ -832,10 +832,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>100</v>
@@ -908,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="1">
         <v>5</v>
@@ -949,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1">
         <v>5</v>
@@ -987,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1">
         <v>5</v>

--- a/Datas/PackageSetData.xlsx
+++ b/Datas/PackageSetData.xlsx
@@ -681,7 +681,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
         <v>100</v>
@@ -720,7 +720,7 @@
         <v>3</v>
       </c>
       <c r="F5" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
         <v>100</v>
@@ -755,10 +755,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>100</v>
@@ -794,10 +794,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>100</v>
@@ -832,10 +832,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>100</v>
